--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC46701-1B81-4C29-855E-9FC46B1FF73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC35C866-84FB-4BEB-B8EC-D536D8581994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>productive day.</t>
+  </si>
+  <si>
+    <t>quite good.</t>
+  </si>
+  <si>
+    <t>it was a good day.</t>
+  </si>
+  <si>
+    <t>unique day it was.</t>
+  </si>
+  <si>
+    <t>had regular classes and completed a little study at night.</t>
   </si>
 </sst>
 </file>
@@ -1468,114 +1480,234 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="14">
+        <v>300</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>150</v>
+      </c>
+      <c r="E16" s="14">
+        <v>20</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>610</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>830</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>25</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>815</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>45</v>
+      </c>
+      <c r="F18" s="14">
+        <v>100</v>
+      </c>
+      <c r="G18" s="14">
+        <v>2</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="14">
+        <v>300</v>
+      </c>
+      <c r="C19" s="14">
+        <v>25</v>
+      </c>
+      <c r="D19" s="14">
+        <v>150</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>435</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>20</v>
+      </c>
+      <c r="F20" s="14">
+        <v>200</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>180</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC35C866-84FB-4BEB-B8EC-D536D8581994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E447ED-CE5A-4956-A66C-F71FA6272456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1709,27 +1709,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E447ED-CE5A-4956-A66C-F71FA6272456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55C1906-3CB8-49DB-9861-421EB2065011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>had regular classes and completed a little study at night.</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
@@ -1756,26 +1759,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>40</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>150</v>
+      </c>
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55C1906-3CB8-49DB-9861-421EB2065011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982F4F70-99C8-4E92-A0CE-DE727988E3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,7 +241,10 @@
     <t>had regular classes and completed a little study at night.</t>
   </si>
   <si>
-    <t>c</t>
+    <t>unpredictable dat it was.</t>
+  </si>
+  <si>
+    <t>good  day.</t>
   </si>
 </sst>
 </file>
@@ -1805,26 +1808,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>20</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982F4F70-99C8-4E92-A0CE-DE727988E3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC47F6E-0E65-430C-B079-7F31B6432D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>good  day.</t>
+  </si>
+  <si>
+    <t>nothing.</t>
   </si>
 </sst>
 </file>
@@ -1854,26 +1857,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
+        <v>240</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>705</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC47F6E-0E65-430C-B079-7F31B6432D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A56F45-BFCC-4E35-9BB9-163918EE8495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>nothing.</t>
+  </si>
+  <si>
+    <t>learn something new.</t>
   </si>
 </sst>
 </file>
@@ -1903,26 +1906,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>25</v>
+      </c>
+      <c r="F25" s="14">
+        <v>100</v>
+      </c>
+      <c r="G25" s="14">
+        <v>2</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>785</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>655</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A56F45-BFCC-4E35-9BB9-163918EE8495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833E9190-885D-4B71-89AA-F93B8B739A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>learn something new.</t>
+  </si>
+  <si>
+    <t>felt a bit tired after evening classes.</t>
   </si>
 </sst>
 </file>
@@ -1951,30 +1954,56 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>40</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>40</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>120</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13">
+        <v>46267</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833E9190-885D-4B71-89AA-F93B8B739A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81275916-5B2D-4E17-A82D-EAA0844FF906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>felt a bit tired after evening classes.</t>
+  </si>
+  <si>
+    <t>I have done my frist presenation on Topic in PEL class.</t>
   </si>
 </sst>
 </file>
@@ -2000,29 +2003,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
         <v>46267</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="B27" s="14">
+        <v>300</v>
+      </c>
+      <c r="C27" s="14">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>240</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81275916-5B2D-4E17-A82D-EAA0844FF906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527628D5-CDF7-4CF9-96A6-992A538C8B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,7 +256,10 @@
     <t>felt a bit tired after evening classes.</t>
   </si>
   <si>
-    <t>I have done my frist presenation on Topic in PEL class.</t>
+    <t>I have done my first presenation on a Topic in PEL class.</t>
+  </si>
+  <si>
+    <t>good day.</t>
   </si>
 </sst>
 </file>
@@ -443,7 +446,31 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2050,29 +2077,55 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>40</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13">
+        <v>46269</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -10286,8 +10339,13 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J27 J29:J401">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527628D5-CDF7-4CF9-96A6-992A538C8B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C006DF-70E4-4974-80B9-38D139B729CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,6 +261,9 @@
   <si>
     <t>good day.</t>
   </si>
+  <si>
+    <t>today I done an interaction session with our dean.</t>
+  </si>
 </sst>
 </file>
 
@@ -446,31 +449,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2122,29 +2101,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <v>46269</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="B29" s="14">
+        <v>300</v>
+      </c>
+      <c r="C29" s="14">
+        <v>40</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>250</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" ref="I29" si="2">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <v>920</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" ref="J29" si="3">IF(I29="","",1440-I29)</f>
+        <v>520</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
@@ -3036,11 +3037,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3058,11 +3059,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3080,11 +3081,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3102,11 +3103,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3124,11 +3125,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3146,11 +3147,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3168,11 +3169,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3190,11 +3191,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3212,11 +3213,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3234,11 +3235,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3256,11 +3257,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3278,11 +3279,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3300,11 +3301,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3322,11 +3323,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3344,11 +3345,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3366,11 +3367,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3388,11 +3389,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3410,11 +3411,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3432,11 +3433,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3454,11 +3455,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3476,11 +3477,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3498,11 +3499,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3520,11 +3521,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3542,11 +3543,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3564,11 +3565,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3586,11 +3587,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3608,11 +3609,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3630,11 +3631,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3652,11 +3653,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3674,11 +3675,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3696,11 +3697,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3718,11 +3719,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3740,11 +3741,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3762,11 +3763,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3784,11 +3785,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3806,11 +3807,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3828,11 +3829,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3850,11 +3851,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3872,11 +3873,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3894,11 +3895,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3916,11 +3917,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3938,11 +3939,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3960,11 +3961,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3982,11 +3983,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4004,11 +4005,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4026,11 +4027,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4048,11 +4049,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4070,11 +4071,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4092,11 +4093,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4114,11 +4115,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4136,11 +4137,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4158,11 +4159,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4180,11 +4181,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4202,11 +4203,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4224,11 +4225,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4246,11 +4247,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4268,11 +4269,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4290,11 +4291,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4312,11 +4313,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4334,11 +4335,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4356,11 +4357,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4378,11 +4379,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4400,11 +4401,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4422,11 +4423,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4444,11 +4445,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4466,11 +4467,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4488,11 +4489,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4510,11 +4511,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4532,11 +4533,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4554,11 +4555,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4576,11 +4577,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4598,11 +4599,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4620,11 +4621,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4642,11 +4643,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4664,11 +4665,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4686,11 +4687,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4708,11 +4709,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4730,11 +4731,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4752,11 +4753,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4774,11 +4775,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4796,11 +4797,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4818,11 +4819,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4840,11 +4841,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4862,11 +4863,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4884,11 +4885,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4906,11 +4907,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4928,11 +4929,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4950,11 +4951,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4972,11 +4973,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4994,11 +4995,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5016,11 +5017,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5038,11 +5039,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5060,11 +5061,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5082,11 +5083,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5104,11 +5105,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5126,11 +5127,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5148,11 +5149,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5170,11 +5171,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5192,11 +5193,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5214,11 +5215,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5236,11 +5237,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5258,11 +5259,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5280,11 +5281,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5302,11 +5303,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5324,11 +5325,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5346,11 +5347,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5368,11 +5369,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5390,11 +5391,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5412,11 +5413,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5434,11 +5435,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5456,11 +5457,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5478,11 +5479,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5500,11 +5501,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5522,11 +5523,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5544,11 +5545,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5566,11 +5567,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5588,11 +5589,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5610,11 +5611,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5632,11 +5633,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5654,11 +5655,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5676,11 +5677,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5698,11 +5699,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5720,11 +5721,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5742,11 +5743,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5764,11 +5765,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5786,11 +5787,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5808,11 +5809,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5830,11 +5831,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5852,11 +5853,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5874,11 +5875,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5896,11 +5897,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5918,11 +5919,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5940,11 +5941,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5962,11 +5963,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5984,11 +5985,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6006,11 +6007,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6028,11 +6029,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6050,11 +6051,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6072,11 +6073,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6094,11 +6095,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6116,11 +6117,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6138,11 +6139,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6160,11 +6161,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6182,11 +6183,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6204,11 +6205,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6226,11 +6227,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6248,11 +6249,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6270,11 +6271,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6292,11 +6293,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6314,11 +6315,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6336,11 +6337,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6358,11 +6359,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6380,11 +6381,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6402,11 +6403,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6424,11 +6425,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6446,11 +6447,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6468,11 +6469,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6490,11 +6491,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6512,11 +6513,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6534,11 +6535,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6556,11 +6557,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6578,11 +6579,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6600,11 +6601,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6622,11 +6623,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6644,11 +6645,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6666,11 +6667,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6688,11 +6689,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6710,11 +6711,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6732,11 +6733,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6754,11 +6755,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6776,11 +6777,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6798,11 +6799,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6820,11 +6821,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6842,11 +6843,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6864,11 +6865,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6886,11 +6887,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6908,11 +6909,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6930,11 +6931,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6952,11 +6953,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6974,11 +6975,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6996,11 +6997,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7018,11 +7019,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7040,11 +7041,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7062,11 +7063,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7084,11 +7085,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7106,11 +7107,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7128,11 +7129,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7150,11 +7151,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7172,11 +7173,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7194,11 +7195,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7216,11 +7217,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7238,11 +7239,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7260,11 +7261,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7282,11 +7283,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7304,11 +7305,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7326,11 +7327,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7348,11 +7349,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7370,11 +7371,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7392,11 +7393,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7414,11 +7415,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7436,11 +7437,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7458,11 +7459,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7480,11 +7481,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7502,11 +7503,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7524,11 +7525,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7546,11 +7547,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7568,11 +7569,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7590,11 +7591,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7612,11 +7613,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7634,11 +7635,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7656,11 +7657,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7678,11 +7679,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7700,11 +7701,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7722,11 +7723,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7744,11 +7745,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7766,11 +7767,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7788,11 +7789,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7810,11 +7811,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7832,11 +7833,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7854,11 +7855,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7876,11 +7877,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7898,11 +7899,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7920,11 +7921,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7942,11 +7943,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7964,11 +7965,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7986,11 +7987,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8008,11 +8009,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8030,11 +8031,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8052,11 +8053,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8074,11 +8075,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8096,11 +8097,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8118,11 +8119,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8140,11 +8141,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8162,11 +8163,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8184,11 +8185,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8206,11 +8207,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8228,11 +8229,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8250,11 +8251,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8272,11 +8273,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8294,11 +8295,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8316,11 +8317,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8338,11 +8339,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8360,11 +8361,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8382,11 +8383,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8404,11 +8405,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8426,11 +8427,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8448,11 +8449,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8470,11 +8471,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8492,11 +8493,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8514,11 +8515,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8536,11 +8537,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8558,11 +8559,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8580,11 +8581,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8602,11 +8603,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8624,11 +8625,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8646,11 +8647,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8668,11 +8669,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8690,11 +8691,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8712,11 +8713,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8734,11 +8735,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8756,11 +8757,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8778,11 +8779,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8800,11 +8801,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8822,11 +8823,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8844,11 +8845,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8866,11 +8867,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8888,11 +8889,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8910,11 +8911,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8932,11 +8933,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8954,11 +8955,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8976,11 +8977,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8998,11 +8999,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9020,11 +9021,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9042,11 +9043,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9064,11 +9065,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9086,11 +9087,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9108,11 +9109,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9130,11 +9131,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9152,11 +9153,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9174,11 +9175,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9196,11 +9197,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9218,11 +9219,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9240,11 +9241,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9262,11 +9263,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9284,11 +9285,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9306,11 +9307,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9328,11 +9329,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9350,11 +9351,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9372,11 +9373,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9394,11 +9395,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9416,11 +9417,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9438,11 +9439,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9460,11 +9461,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9482,11 +9483,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9504,11 +9505,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9526,11 +9527,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9548,11 +9549,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9570,11 +9571,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9592,11 +9593,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9614,11 +9615,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9636,11 +9637,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9658,11 +9659,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9680,11 +9681,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9702,11 +9703,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9724,11 +9725,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9746,11 +9747,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9768,11 +9769,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9790,11 +9791,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9812,11 +9813,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9834,11 +9835,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9856,11 +9857,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9878,11 +9879,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9900,11 +9901,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9922,11 +9923,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9944,11 +9945,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9966,11 +9967,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9988,11 +9989,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10010,11 +10011,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10032,11 +10033,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10054,11 +10055,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10076,11 +10077,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10098,11 +10099,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10120,11 +10121,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10142,11 +10143,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10164,11 +10165,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10186,11 +10187,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10208,11 +10209,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10230,11 +10231,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10252,11 +10253,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10274,11 +10275,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10296,11 +10297,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10318,11 +10319,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -10339,12 +10340,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J27 J29:J401">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
+  <conditionalFormatting sqref="J6:J401">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/CAP766(PYTHON).xlsx
+++ b/CAP766(PYTHON).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C006DF-70E4-4974-80B9-38D139B729CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A26688-A0B3-4C5C-A6D5-FC6ACC4E35DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>today I done an interaction session with our dean.</t>
+  </si>
+  <si>
+    <t>…..........</t>
   </si>
 </sst>
 </file>
@@ -2148,26 +2151,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="14">
+        <v>360</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>150</v>
+      </c>
+      <c r="E30" s="14">
+        <v>20</v>
+      </c>
+      <c r="F30" s="14">
+        <v>50</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
